--- a/public/reports/EVedhika_UBD_Daily_PC_Report_2026-10-29.xlsx
+++ b/public/reports/EVedhika_UBD_Daily_PC_Report_2026-10-29.xlsx
@@ -433,7 +433,7 @@
         <v>Report Generated At</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-10-29 02:23:24 IST</v>
+        <v>2026-10-29 20:37:26 IST</v>
       </c>
     </row>
     <row r="5">
